--- a/artfynd/A 60176-2021 artfynd.xlsx
+++ b/artfynd/A 60176-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60176-2021 artfynd.xlsx
+++ b/artfynd/A 60176-2021 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 60176-2021 artfynd.xlsx
+++ b/artfynd/A 60176-2021 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 60176-2021 artfynd.xlsx
+++ b/artfynd/A 60176-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66637971</v>
+        <v>6767444</v>
       </c>
       <c r="B2" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107644</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>1129</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tistelsnyltrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Orobanche reticulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fädernet söder om, Vg</t>
+          <t>Smedstorp nordost, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>427583</v>
+        <v>427769</v>
       </c>
       <c r="R2" t="n">
-        <v>6479479</v>
+        <v>6479194</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-07-09</t>
+          <t>2010-07-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-07-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Slåttervallar, trädesåkrar,damm, högörtsäng och vägkanter</t>
+          <t>2010-07-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,31 +769,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
           <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Billingens flora</t>
-        </is>
-      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66638013</v>
+        <v>6767777</v>
       </c>
       <c r="B3" t="n">
-        <v>106496</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>107644</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -831,14 +821,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fädernet söder om, Vg</t>
+          <t>Smedstorp nordost, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427735</v>
+        <v>427758</v>
       </c>
       <c r="R3" t="n">
-        <v>6479444</v>
+        <v>6479299</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,17 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-07-09</t>
+          <t>2010-07-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-07-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Slåttervallar, trädesåkrar,damm, högörtsäng och vägkanter</t>
+          <t>2010-07-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,69 +875,69 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Billingens flora</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102988229</v>
+        <v>6767778</v>
       </c>
       <c r="B4" t="n">
-        <v>108691</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107644</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220228</v>
+        <v>1129</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Tistelsnyltrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Orobanche reticulata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fädernet syd, Vg</t>
+          <t>Smedstorp nordost, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427635</v>
+        <v>427753</v>
       </c>
       <c r="R4" t="n">
-        <v>6479428</v>
+        <v>6479345</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2004-08-08</t>
+          <t>2010-07-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2004-08-08</t>
+          <t>2010-07-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,24 +977,1536 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Fuktäng</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6767779</v>
+      </c>
+      <c r="B5" t="n">
+        <v>107644</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1129</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tistelsnyltrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Orobanche reticulata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Smedstorp nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>427753</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6479370</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2010-07-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2010-07-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6767780</v>
+      </c>
+      <c r="B6" t="n">
+        <v>107644</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1129</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tistelsnyltrot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Orobanche reticulata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Smedstorp nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>427753</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6479388</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2010-07-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2010-07-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6767782</v>
+      </c>
+      <c r="B7" t="n">
+        <v>107644</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1129</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tistelsnyltrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Orobanche reticulata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Smedstorp nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>427747</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6479462</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2010-07-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2010-07-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>66638013</v>
+      </c>
+      <c r="B8" t="n">
+        <v>107644</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1129</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tistelsnyltrot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Orobanche reticulata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fädernet söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>427735</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6479444</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2017-07-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2017-07-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Slåttervallar, trädesåkrar,damm, högörtsäng och vägkanter</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>102988203</v>
+      </c>
+      <c r="B9" t="n">
+        <v>107644</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1129</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tistelsnyltrot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Orobanche reticulata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fädernet öst Väg 2752, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>427760</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6479329</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2007-07-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2007-07-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Kurt-Anders Johansson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>102988204</v>
+      </c>
+      <c r="B10" t="n">
+        <v>107644</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1129</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tistelsnyltrot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Orobanche reticulata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fädernet öst Väg 2752, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>427758</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6479358</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2007-07-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2007-07-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>102988205</v>
+      </c>
+      <c r="B11" t="n">
+        <v>107644</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1129</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tistelsnyltrot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Orobanche reticulata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fädernet öst Väg 2752, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>427746</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6479436</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2007-07-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2007-07-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>64423406</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Toresäter öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>427756</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6479349</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2010-06-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2010-06-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Väg 2752 - Vägdiken sträckan Toresäter öster om</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>66637968</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fädernet söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>427541</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6479485</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2017-07-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2017-07-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Slåttervallar, trädesåkrar,damm, högörtsäng och vägkanter</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>64423405</v>
+      </c>
+      <c r="B14" t="n">
+        <v>108194</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Toresäter öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>427753</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6479422</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2010-06-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2010-06-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Väg 2752 - Vägdiken sträckan Toresäter öster om</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134371077</v>
+      </c>
+      <c r="B15" t="n">
+        <v>108275</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fädernet, S om, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>427749</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6479455</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Karin Kjellberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Karin Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>102988229</v>
+      </c>
+      <c r="B16" t="n">
+        <v>109866</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fädernet syd, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>427635</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6479428</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2004-08-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2004-08-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Fuktäng</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>64423257</v>
+      </c>
+      <c r="B17" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Toresäter öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>427747</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6479353</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2010-06-24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2010-06-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Väg 2752 - Vägdiken sträckan Toresäter öster om</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>66637971</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fädernet söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>427583</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6479479</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2017-07-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2017-07-09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Slåttervallar, trädesåkrar,damm, högörtsäng och vägkanter</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
         <is>
           <t>Billingens flora</t>
         </is>

--- a/artfynd/A 60176-2021 artfynd.xlsx
+++ b/artfynd/A 60176-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6767444</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6767777</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6767778</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6767779</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6767780</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6767782</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1423,6 +1458,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66638013</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1529,6 +1569,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102988203</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102988204</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1741,6 +1791,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102988205</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1856,6 +1911,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64423406</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1971,6 +2031,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66637968</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2086,6 +2151,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64423405</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2192,6 +2262,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134371077</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2298,6 +2373,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102988229</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2405,6 +2485,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64423257</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2511,8 +2596,32 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66637971</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>